--- a/presentation/UserFeedback.xlsx
+++ b/presentation/UserFeedback.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ad1c0a53281c2ab/Documents/University/Studies/Sem 5/Practical Electronics/pe04/presentation/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Projects\pe04\presentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B2A70182-7874-431E-9B39-9487D7CD76D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08DE2D4D-5CF0-4CDF-9C37-3B655572C8D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F6B5E1E7-0962-40FF-A1BA-66C688150A37}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{F6B5E1E7-0962-40FF-A1BA-66C688150A37}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="23">
   <si>
     <t>User Feedback</t>
   </si>
@@ -93,6 +93,18 @@
   </si>
   <si>
     <t>Different shapes for housing</t>
+  </si>
+  <si>
+    <t>Housing slides too much</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Using rubber pads on bottom of housing </t>
+  </si>
+  <si>
+    <t>Could be implemented into a mailbox</t>
+  </si>
+  <si>
+    <t>Door can easily be pulled open</t>
   </si>
 </sst>
 </file>
@@ -132,7 +144,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -216,21 +228,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -251,17 +248,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -289,9 +275,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -301,14 +293,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -643,126 +627,211 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E5901A2-E583-452B-8260-88BE4A7B89C7}">
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="45.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="45.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="24.75" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="4"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="10"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="10">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <v>1</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="3">
         <v>9</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
         <v>2</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="4">
         <v>9</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
         <v>3</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="4">
         <v>9</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
         <v>4</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="4">
         <v>9</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
         <v>5</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="4">
         <v>9.5</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="2" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
+        <v>6</v>
+      </c>
+      <c r="B8" s="4">
+        <v>9</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4">
+        <v>10</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10" s="4">
+        <v>9.5</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="4">
+        <v>10</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
+        <v>10</v>
+      </c>
+      <c r="B12" s="4">
+        <v>9</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
